--- a/data/sample/level1_marksheet_2025_dec.xlsx
+++ b/data/sample/level1_marksheet_2025_dec.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,12 +483,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ST2023-0022</t>
+          <t>ST2023-0119</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Susan Rogers</t>
+          <t>Katie Anderson</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -504,7 +504,7 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
@@ -513,12 +513,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ST2023-0119</t>
+          <t>ST2023-0130</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Katie Anderson</t>
+          <t>James Collins</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -535,7 +535,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
@@ -543,12 +543,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ST2023-0138</t>
+          <t>ST2023-0142</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pasindu Liyanage</t>
+          <t>Nuwan Abeysekera</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -561,10 +561,10 @@
           <t>2023-Jul</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="n">
-        <v>52</v>
-      </c>
+      <c r="E4" t="n">
+        <v>37</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
@@ -573,12 +573,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ST2023-0142</t>
+          <t>ST2023-0481</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nuwan Abeysekera</t>
+          <t>Pasindu Perera</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -591,10 +591,10 @@
           <t>2023-Jul</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>24</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>59</v>
+      </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
@@ -603,12 +603,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ST2023-0145</t>
+          <t>ST2024-0160</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Chaminda Senanayake</t>
+          <t>Kasun Samarasinghe</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -618,13 +618,13 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2023-Jul</t>
+          <t>2024-Jan</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>29</v>
+        <v>74</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
@@ -633,29 +633,29 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ST2023-0218</t>
+          <t>ST2024-0167</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Christopher Lopez</t>
+          <t>Richard Morgan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Diploma in Accounting</t>
+          <t>Diploma in Taxation</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2023-Jan</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
+          <t>2024-Jan</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>66</v>
+      </c>
       <c r="F7" t="inlineStr"/>
-      <c r="G7" t="n">
-        <v>51</v>
-      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
@@ -663,12 +663,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ST2023-0221</t>
+          <t>ST2024-0198</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Pasindu Gunasekara</t>
+          <t>Shanika Samarasinghe</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -678,13 +678,13 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2023-Jul</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="n">
-        <v>46</v>
-      </c>
+          <t>2024-Jul</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>80</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
@@ -693,12 +693,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ST2023-0270</t>
+          <t>ST2024-0226</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Amaya Fernando</t>
+          <t>Brooke Harvey</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2023-Jan</t>
+          <t>2024-Jul</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
@@ -723,12 +723,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ST2023-0303</t>
+          <t>ST2024-0293</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>John Garcia</t>
+          <t>Ishara Dissanayake</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -738,13 +738,13 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2023-Jul</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="n">
-        <v>55</v>
-      </c>
+          <t>2024-Jul</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
@@ -753,42 +753,42 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ST2023-0304</t>
+          <t>ST2024-0305</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kimberly Henson</t>
+          <t>Ruwan Ratnayake</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Diploma in Accounting</t>
+          <t>Diploma in Business Management</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2023-Jul</t>
+          <t>2024-Jul</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
-      <c r="G11" t="n">
-        <v>60</v>
-      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="n">
+        <v>67</v>
+      </c>
       <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ST2023-0384</t>
+          <t>ST2024-0358</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lahiru Fernando</t>
+          <t>Chaminda Bandara</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -798,14 +798,16 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2023-Jul</t>
+          <t>2024-Jan</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="n">
+        <v>66</v>
+      </c>
       <c r="H12" t="n">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
@@ -813,29 +815,29 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ST2023-0422</t>
+          <t>ST2024-0370</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>James Johnson</t>
+          <t>Lahiru Herath</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Diploma in Accounting</t>
+          <t>Diploma in Taxation</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2023-Jan</t>
+          <t>2024-Jul</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="n">
-        <v>25</v>
-      </c>
+      <c r="F13" t="n">
+        <v>68</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
@@ -843,162 +845,168 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ST2023-0473</t>
+          <t>ST2024-0388</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Malsha Gunasekara</t>
+          <t>Dilshan Amarasinghe</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Diploma in Accounting</t>
+          <t>Diploma in Taxation</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2023-Jan</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
+          <t>2024-Jul</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>73</v>
+      </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="n">
-        <v>52</v>
-      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ST2023-0517</t>
+          <t>ST2024-0391</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Isuru Ratnayake</t>
+          <t>Buddhika Karunaratne</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Diploma in Taxation</t>
+          <t>Diploma in Accounting</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2023-Jul</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>47</v>
-      </c>
+          <t>2024-Jan</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ST2023-0548</t>
+          <t>ST2024-0406</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Chaminda Karunaratne</t>
+          <t>Thomas Santana</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Diploma in Business Management</t>
+          <t>Diploma in Taxation</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2023-Jan</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
+          <t>2024-Jul</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>69</v>
+      </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="n">
-        <v>50</v>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ST2023-0558</t>
+          <t>ST2024-0448</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Susan Sanders</t>
+          <t>Kasun Weerasinghe</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Diploma in Taxation</t>
+          <t>Diploma in Business Management</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2023-Jul</t>
+          <t>2024-Jan</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
-      <c r="F17" t="n">
-        <v>63</v>
-      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ST2024-0053</t>
+          <t>ST2024-0463</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Buddhika De Mel</t>
+          <t>Katie Boyd</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Diploma in Accounting</t>
+          <t>Diploma in Taxation</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2024-Jan</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
+          <t>2024-Jul</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>51</v>
+      </c>
+      <c r="F18" t="n">
+        <v>53</v>
+      </c>
       <c r="G18" t="inlineStr"/>
-      <c r="H18" t="n">
-        <v>54</v>
-      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ST2024-0118</t>
+          <t>ST2024-0502</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Chad Hodges</t>
+          <t>Jeffrey Robinson</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1008,12 +1016,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2024-Jan</t>
+          <t>2024-Jul</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
@@ -1023,12 +1031,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ST2024-0160</t>
+          <t>ST2024-0540</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Kasun Samarasinghe</t>
+          <t>Kamal Bandara</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1044,26 +1052,28 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
-        <v>59</v>
-      </c>
-      <c r="H20" t="inlineStr"/>
+        <v>66</v>
+      </c>
+      <c r="H20" t="n">
+        <v>37</v>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ST2024-0162</t>
+          <t>ST2024-0577</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Collin Jordan</t>
+          <t>Nadeesha Karunaratne</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Diploma in Taxation</t>
+          <t>Diploma in Accounting</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1071,24 +1081,24 @@
           <t>2024-Jul</t>
         </is>
       </c>
-      <c r="E21" t="n">
-        <v>72</v>
-      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="H21" t="n">
+        <v>59</v>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ST2024-0167</t>
+          <t>ST2024-0585</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Richard Morgan</t>
+          <t>Kavindi Dissanayake</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1098,13 +1108,13 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2024-Jan</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>48</v>
-      </c>
-      <c r="F22" t="inlineStr"/>
+          <t>2024-Jul</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="n">
+        <v>66</v>
+      </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
@@ -1113,17 +1123,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ST2024-0224</t>
+          <t>ST2024-0599</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Madushan Jayawardena</t>
+          <t>Nicole Sanchez</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Diploma in Accounting</t>
+          <t>Diploma in Taxation</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1131,678 +1141,14 @@
           <t>2024-Jul</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="n">
+        <v>69</v>
+      </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
-      <c r="H23" t="n">
-        <v>46</v>
-      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>ST2024-0275</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Dilshan Abeysekera</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Diploma in Accounting</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2024-Jan</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="n">
-        <v>50</v>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>ST2024-0279</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Madushan Herath</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Diploma in Accounting</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2024-Jul</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="n">
-        <v>54</v>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>ST2024-0336</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Monica Garrison</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Diploma in Taxation</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2024-Jan</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="n">
-        <v>50</v>
-      </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>ST2024-0340</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Kasun Abeysekera</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Diploma in Taxation</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2024-Jul</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>79</v>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>ST2024-0343</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Gayani Jayawardena</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Diploma in Taxation</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2024-Jan</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>52</v>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>ST2024-0347</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Mark Lin</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Diploma in Accounting</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2024-Jul</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="n">
-        <v>69</v>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>ST2024-0370</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Lahiru Herath</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Diploma in Taxation</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2024-Jul</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>49</v>
-      </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>ST2024-0383</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Kyle Ortiz</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Diploma in Accounting</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2024-Jan</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="n">
-        <v>48</v>
-      </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>ST2024-0388</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Dilshan Amarasinghe</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Diploma in Taxation</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2024-Jul</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>57</v>
-      </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>ST2024-0403</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Diana Marshall</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Diploma in Taxation</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2024-Jan</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="n">
-        <v>65</v>
-      </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>ST2024-0406</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Thomas Santana</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Diploma in Taxation</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>2024-Jul</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>67</v>
-      </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>ST2024-0411</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Nadeesha Silva</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Diploma in Accounting</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2024-Jan</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="n">
-        <v>49</v>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>ST2024-0420</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Emily Walker</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Diploma in Accounting</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2024-Jul</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="n">
-        <v>61</v>
-      </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>ST2024-0425</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Nuwan Amarasinghe</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Diploma in Accounting</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>2024-Jan</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="n">
-        <v>62</v>
-      </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>ST2024-0463</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Katie Boyd</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Diploma in Taxation</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>2024-Jul</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>51</v>
-      </c>
-      <c r="F38" t="n">
-        <v>52</v>
-      </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>ST2024-0479</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Jasmine Brown</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Diploma in Accounting</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>2024-Jan</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="n">
-        <v>38</v>
-      </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>ST2024-0508</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Tanner Anderson</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Diploma in Taxation</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>2024-Jan</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>42</v>
-      </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>ST2024-0528</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Zoe Bell</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Diploma in Accounting</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>2024-Jul</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="n">
-        <v>61</v>
-      </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>ST2024-0540</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Kamal Bandara</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Diploma in Accounting</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>2024-Jan</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="n">
-        <v>39</v>
-      </c>
-      <c r="H42" t="n">
-        <v>46</v>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>ST2024-0541</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Ishara Samarasinghe</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Diploma in Taxation</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>2024-Jul</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="n">
-        <v>71</v>
-      </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>ST2024-0554</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Daniel Johnson</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Diploma in Taxation</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>2024-Jul</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="n">
-        <v>57</v>
-      </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>ST2024-0599</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Nicole Sanchez</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Diploma in Taxation</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>2024-Jul</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="n">
-        <v>55</v>
-      </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
